--- a/processors/shipping_bill/templates/Book8.xlsx
+++ b/processors/shipping_bill/templates/Book8.xlsx
@@ -417,37 +417,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AA1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.5703125" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="16.140625" customWidth="1" min="3" max="3"/>
     <col width="45.5703125" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="14.7109375" customWidth="1" min="7" max="7"/>
-    <col width="17.7109375" customWidth="1" min="8" max="8"/>
-    <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="5" customWidth="1" min="10" max="10"/>
-    <col width="6" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="8.85546875" customWidth="1" min="15" max="15"/>
-    <col width="11.28515625" customWidth="1" min="16" max="16"/>
-    <col width="8.85546875" customWidth="1" min="17" max="17"/>
-    <col width="9" customWidth="1" min="18" max="18"/>
+    <col width="14.7109375" customWidth="1" min="5" max="5"/>
+    <col width="17.7109375" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="5" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="8.85546875" customWidth="1" min="14" max="14"/>
+    <col width="11.28515625" customWidth="1" min="15" max="15"/>
+    <col width="8.85546875" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="11.5703125" customWidth="1" min="18" max="18"/>
     <col width="11.5703125" customWidth="1" min="19" max="19"/>
-    <col width="11.5703125" customWidth="1" min="20" max="20"/>
-    <col width="9.7109375" customWidth="1" min="21" max="21"/>
-    <col width="10" customWidth="1" min="22" max="22"/>
-    <col width="18.7109375" customWidth="1" min="23" max="23"/>
-    <col width="10" customWidth="1" min="24" max="24"/>
-    <col width="5" customWidth="1" min="25" max="25"/>
-    <col width="8.5703125" customWidth="1" min="26" max="26"/>
-    <col width="11" customWidth="1" min="27" max="27"/>
-    <col width="12" customWidth="1" min="28" max="28"/>
+    <col width="9.7109375" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="21" max="21"/>
+    <col width="18.7109375" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="5" customWidth="1" min="24" max="24"/>
+    <col width="8.5703125" customWidth="1" min="25" max="25"/>
+    <col width="11" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -473,120 +472,115 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>By Name3</t>
+          <t>Port of Discharge</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>By Name4</t>
+          <t>Country of Discharge</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Port of Discharge</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Country of Discharge</t>
+          <t>Qty</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Qty</t>
+          <t>UOM</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>UOM</t>
+          <t>Rate</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Rate</t>
+          <t>FC Value</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>FC Value</t>
+          <t>FOB VALUE (FC)</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>FOB VALUE (FC)</t>
+          <t>Freight</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Freight</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Commission</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Commission</t>
+          <t>Port Code</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Port Code</t>
+          <t>SB No.</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>SB No.</t>
+          <t>SB.Date</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>SB.Date</t>
+          <t>LEO DATE</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>LEO DATE</t>
+          <t>DBK Claim</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>DBK Claim</t>
+          <t>RODTEP AMT</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>RODTEP AMT</t>
+          <t>Scheme Description</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>Scheme Description</t>
+          <t>HS CD</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>HS CD</t>
+          <t>S</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>DBK Rate (%)</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>DBK Rate (%)</t>
+          <t>DBK AMT</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>DBK AMT</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Exchange Rate</t>
         </is>
